--- a/01_propulsion_fmea/propulsion_fmea.xlsx
+++ b/01_propulsion_fmea/propulsion_fmea.xlsx
@@ -625,7 +625,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Part Family: Drone Propulsion System   |   Revision: A   |   Date: 2026-06-03   |   Owner: Quality Engineering</t>
+          <t>Part Family: Drone Propulsion System   |   Revision: A   |   Date: 2026-06-04   |   Owner: Quality Engineering</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="Q5" s="5" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Q6" s="9" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="P7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Q7" s="5" t="n">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Q8" s="9" t="n">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="P9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="Q9" s="5" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Q10" s="9" t="n">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="P11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="Q11" s="5" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="P12" s="9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Q12" s="9" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Q13" s="5" t="n">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="P14" s="9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Q14" s="9" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="P15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Q15" s="5" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="P16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="Q16" s="9" t="n">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="P17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="Q17" s="5" t="n">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="P18" s="9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Q18" s="9" t="n">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="P19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Q19" s="5" t="n">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="P20" s="9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Q20" s="9" t="n">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="P21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Q21" s="5" t="n">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="P22" s="9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Q22" s="9" t="n">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="P23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="Q23" s="5" t="n">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="P24" s="9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Q24" s="9" t="n">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Q25" s="5" t="n">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P26" s="9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Q26" s="9" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="P27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="Q27" s="5" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="P28" s="9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Q28" s="9" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="P29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="Q29" s="5" t="n">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="P30" s="9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Q30" s="9" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Q31" s="5" t="n">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="P32" s="9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Q32" s="9" t="n">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="P33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Q33" s="5" t="n">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="P34" s="9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Q34" s="9" t="n">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Q35" s="5" t="n">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="P36" s="9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Q36" s="9" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="P37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Q37" s="5" t="n">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="P38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="Q38" s="9" t="n">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="P39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Q39" s="5" t="n">
